--- a/ksoft_old/docs/fields_details/jalmeida/CE0302.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302.xlsx
@@ -2008,13 +2008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BA837F2-83DF-4242-96AB-F269D62D8037}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9D89830-A43E-43EA-987B-CCB5F9541C1C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01E6118-617C-4671-BC00-CF9706C4397A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A153F302-875B-490F-B526-0CA233FD9704}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455540EB-19BD-493F-868A-82105606B4A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099FD400-ECE5-4D52-98DA-034EAE1B0584}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CE0302.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302.xlsx
@@ -2008,13 +2008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9D89830-A43E-43EA-987B-CCB5F9541C1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E23439DA-93F5-4C6C-B6E1-B8CD46973E92}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A153F302-875B-490F-B526-0CA233FD9704}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5384CF70-83F7-4B42-86BE-8E6C1BB85B79}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099FD400-ECE5-4D52-98DA-034EAE1B0584}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{589E17BC-993B-4209-B1B1-796AEABF87E4}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CE0302.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CE0302.xlsx
@@ -2008,13 +2008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E23439DA-93F5-4C6C-B6E1-B8CD46973E92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BA837F2-83DF-4242-96AB-F269D62D8037}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5384CF70-83F7-4B42-86BE-8E6C1BB85B79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01E6118-617C-4671-BC00-CF9706C4397A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{589E17BC-993B-4209-B1B1-796AEABF87E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455540EB-19BD-493F-868A-82105606B4A7}"/>
 </file>